--- a/student_data.xlsx
+++ b/student_data.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StudentData" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="student_data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>subjects</t>
+          <t>subject</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -461,29 +461,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>6.3</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -492,106 +492,106 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>5.11</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>6.39</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>DSA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>6.47</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
       <c r="G6" t="n">
-        <v>8.74</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,133 +600,133 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>6.54</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>7.71</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>8.359999999999999</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>DSA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
         <v>9</v>
       </c>
-      <c r="E10" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
       <c r="G10" t="n">
-        <v>7.47</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>8.06</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -735,118 +735,118 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>5.81</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>7.93</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
         <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>5.58</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>DSA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>5.09</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>9</v>
@@ -855,67 +855,67 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>8.66</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>8.31</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>7.66</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -924,133 +924,133 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>7.89</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>DSA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>7.18</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
         <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>8.34</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>6.84</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>8.83</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1059,79 +1059,79 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>5.41</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>DSA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" t="n">
         <v>9</v>
       </c>
-      <c r="F25" t="n">
-        <v>4</v>
-      </c>
       <c r="G25" t="n">
-        <v>5.21</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>8.970000000000001</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1167,25 +1167,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>8.25</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1194,25 +1194,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D29" t="n">
         <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>8.140000000000001</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1221,241 +1221,241 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
-        <v>8.699999999999999</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
         <v>7</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>9.02</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>6.78</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S32</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D33" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>5.98</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S33</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D34" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>5.4</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>DSA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
-        <v>7.74</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>8.42</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D37" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
-        <v>8.869999999999999</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F38" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1464,343 +1464,343 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="D39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>6.26</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>DSA</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D40" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
-        <v>5.86</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>6.73</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="D42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
         <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>7.54</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D43" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>7.24</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>6.81</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>DSA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="D45" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>7.78</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G46" t="n">
-        <v>6.86</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E47" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>5.05</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D48" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E48" t="n">
         <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>8.460000000000001</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D49" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>6.39</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>DSA</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G50" t="n">
-        <v>6.96</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DSA</t>
+          <t>English</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D51" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F51" t="n">
         <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>5.56</v>
+        <v>6.66</v>
       </c>
     </row>
   </sheetData>
